--- a/artfynd/A 59393-2025 artfynd.xlsx
+++ b/artfynd/A 59393-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>99990255</v>
       </c>
       <c r="B2" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600622.2653475759</v>
+        <v>600622</v>
       </c>
       <c r="R2" t="n">
-        <v>6539988.474939723</v>
+        <v>6539988</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -756,19 +751,9 @@
           <t>2022-04-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-04-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
